--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="可比交易案例（初稿）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Wind取数步骤" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Wind导出" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="已剔除" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wind取数步骤" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wind导出" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -483,7 +484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>附件一：同行业可比交易案例（PCB，2023年以来）——公开资料初稿，黄底为待Wind/公告补齐</t>
+          <t>附件一：同行业可比交易案例（PCB，2023年以来）——口径：境内标的；含PCB制造、设备、耗材、材料；含无评估的现金收购。黄底为待Wind/公告补齐</t>
         </is>
       </c>
     </row>
@@ -570,7 +571,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>入选判断</t>
+          <t>标的类别</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -662,7 +663,7 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>入选</t>
+          <t>PCB制造</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -714,7 +715,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>约82,700（最终159亿日元；基础价176.61亿日元约87,000）</t>
+          <t>约82,700（最终159亿日元）</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -754,44 +755,44 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>入选</t>
+          <t>PCB制造（无评估的现金收购）</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>关于收购股权的公告（2022-12-17）。非重大资产重组，可能未披露评估，作价口径需统一</t>
+          <t>关于收购股权的公告（2022-12-17）。非重大资产重组，可能无评估数据</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>300476.SZ</t>
+          <t>688655.SH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>迅捷兴</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>已完成（2023-12付清）</t>
+          <t>预案（2025-04）；后续进展待查</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Pole Star Limited 100%股权（MFS集团）</t>
+          <t>嘉之宏100%股权</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>高多层板、HDI等PCB</t>
+          <t>PCB样板、小批量板</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>柔性电路板、软硬结合板设计、生产及组装（新加坡/马来西亚/中国）</t>
+          <t>柔性电路板FPC（显示模组、新能源电池）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -801,12 +802,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>发行股份及支付现金</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>股权对价3.65亿美元（总成本≤4.6亿美元，含偿债及费用）</t>
+          <t>预案未定价</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -824,9 +825,9 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1,986.64（2024年）</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -834,76 +835,76 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>入选</t>
+          <t>PCB制造</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>关于收购Pole Star Limited 100%股权的公告（2023）及关注函回复。人民币折算汇率、标的净利润待补</t>
+          <t>重组预案（2025-04-10）。若已出草案则取草案数据；若已终止，最新进展填“终止”再定是否保留</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>300476.SZ</t>
+          <t>301362.SZ</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>民爆光电</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>已完成（2024-09）</t>
+          <t>51%已完成（2026-04工商变更）；49%发股部分进行中</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>APCB Electronics (Thailand) 100%股权</t>
+          <t>厦芝精密51%股权（另49%拟发股购买）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>高多层板、HDI等PCB</t>
+          <t>LED照明</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>印制电路板（竞国实业泰国子公司）</t>
+          <t>PCB钻针（载板、AI服务器等高端钻针）</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>横向整合、海外产能布局</t>
+          <t>跨界转型</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>51%现金；49%发行股份</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>27,870</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>锁箱日2024年7月31日</t>
+          <t>24,500（51%部分）</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -911,86 +912,86 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>不适用（标的净资产为负）</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>亏损</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>不适用</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>入选（标的亏损，市盈率不适用）</t>
+          <t>PCB耗材</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>全资子公司收购境外公司并增资的公告（2024-08）。2024年6月末净资产-3,483.2万泰铢</t>
+          <t>发行股份购买资产预案（2026-01-31）及51%股权收购公告。另向标的提供不超过2亿元财务资助</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>688655.SH</t>
+          <t>688308.SH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>迅捷兴</t>
+          <t>欧科亿</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>预案（2025-04）；后续进展待查</t>
+          <t>框架协议（2026-05）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>嘉之宏100%股权</t>
+          <t>永鑫精工51%股权（受让+增资）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PCB样板、小批量板</t>
+          <t>数控刀片、硬质合金棒材</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>柔性电路板FPC（显示模组、新能源电池）</t>
+          <t>PCB微钻、PCB铣刀</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>横向整合、产品线延伸</t>
+          <t>纵向整合（棒材→钻针）</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>发行股份及支付现金</t>
+          <t>100%现金（受让+增资）</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>预案未定价</t>
+          <t>≤42,500（受让≤17,500+增资25,000）</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1008,9 +1009,9 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>1,986.64（2024年）</t>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1028,222 +1029,498 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>待定：看是否出了草案或已终止</t>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>PCB耗材</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>重组预案（2025-04-10）。最终作价、评估及业绩承诺以草案为准；若已终止，按截图口径的“最新进展”填“终止”再决定是否保留</t>
+          <t>股权收购及增资扩股框架协议公告（2026-05-19）；增资投前估值不超过7亿元，审计评估未完成</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>301176.SZ</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>逸豪新材</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>预案（2026-09，定增募资）</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>铭丰电子不低于78%股权（增资收购）</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>电子电路铜箔、铝基覆铜板、PCB</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>电解铜箔（HVLP、载体铜箔、锂电铜箔）</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>定增募资后现金增资收购</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>募资≤180,000；标的全部股权价值约定≤50,000</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>亏损（2026H1净利润-7,800）</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>PCB材料（标的净资产为负）</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>向特定对象发行股票预案（2026-09-21）。2026-06末标的净资产-1.50亿元，资产负债率104.77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>603226.SH</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>菲林格尔</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>拟收购（2026-09-18公告）</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>克锐斯51%股权</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>地板等家居产品</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>PCB压合工序自动化设备（裁切机、铆钉机、预叠线）</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>跨界转型</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>100%现金</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>21,420（暂定）</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>509.22（2025年，未审）</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>约82.5</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>4,625.00</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>约9.08</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>备选：标的是PCB设备，不是PCB制造</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>PCB设备</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>2026-09-18公告及上交所监管工作函。承诺2026–2029年净利润4,000/4,500/5,000/5,000万元</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>以下为2023年以前备选</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>002860.SZ</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>星帅尔</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>停牌筹划（2026-09-21）</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>梵宇科技100%+湘鹰新材料100%股权</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>压缩机用热保护器、起动器等继电器</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>PCB刀具设备（钻针加工中心等）及半成品耗材</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>跨界转型</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>51%现金+49%发行股份</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>84,000（整体估值暂定）</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>7,000.00</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>约12.00</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>PCB设备/耗材</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>停牌公告（2026-09-21）。承诺2026–2028年扣非净利润5,500/7,500/8,000万元；预计不构成重大资产重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>以下为2023年以前备选（案例不够时启用）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>002579.SZ</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>中京电子</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>元盛电子76.12%股权（经珠海亿盛间接+直接收购）</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>刚性PCB、HDI</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>柔性电路板FPC</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>横向整合</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>100%现金</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>33,000</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2017年9月30日</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>2023年前备选（案例不够时启用）</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>2018年完成，整体评估值4.56亿元；2019年再收购剩余45%</t>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>PCB制造，2018年</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>整体评估值4.56亿元；2019年再收购剩余45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>603002.SH</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>宏昌电子</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>无锡宏仁100%股权</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>电子级环氧树脂</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>覆铜板</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>纵向整合</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>发行股份</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>102,900</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>116.03%</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>10,000.00</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>约10.29</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>PCB材料，2020年</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>承诺2020–2022年扣非净利润8,600/9,400/12,000万元</t>
         </is>
       </c>
     </row>
@@ -1253,6 +1530,92 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>证券代码</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>交易</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>剔除原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>300476.SZ</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>胜宏科技</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Pole Star Limited（MFS集团）100%，2023年，现金，股权对价3.65亿美元</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>标的在海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>300476.SZ</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>胜宏科技</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>APCB Electronics (Thailand) 100%，2024年，现金，27,870万元</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>标的在海外</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1309,7 +1672,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>不足5–6个再放宽到2020-01-01</t>
+          <t>标的限境内（海外标的不要）</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1697,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>关键词：标的名称/简介含 电路板、线路板、PCB、FPC、载板、HDI</t>
+          <t>关键词：标的名称/简介含 电路板、线路板、PCB、FPC、载板、HDI、覆铜板、铜箔、电子布、钻针、PCB设备</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>与第3步结果取并集后去重</t>
+          <t>含PCB设备、耗材、材料类标的；非重组的现金收购（无评估）也保留</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>含“受让+增资”合计达到控股的情况</t>
+          <t>含“受让+增资”合计达到控股的情况；支付方式不限（发行股份、可转债、现金或组合均可），不要按支付方式筛</t>
         </is>
       </c>
     </row>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>已完成（2023-11实施）</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>100%现金（股权受让+增资）</t>
+          <t>100%现金（受让10,162.77+增资32,147.53）</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>约42,300</t>
+          <t>42,310.30</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -631,9 +631,9 @@
           <t>2022年12月31日</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -646,9 +646,9 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>12.84（Wind标的方PE，口径待核）</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>重大资产购买及增资暨关联交易报告书（2023-09）；评估值53,631.86万元，扣除期后分红后50,813.84万元。评估方法、标的2022年净利润、有无业绩承诺待核</t>
+          <t>Wind并购重组事件；重大资产购买及增资暨关联交易报告书（2023-09）。标的2022年净利润、有无业绩承诺待核</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>预案（2025-04）；后续进展待查</t>
+          <t>终止（Wind标注失败）</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>PCB制造</t>
+          <t>PCB制造（已终止，建议剔除或仅作参考）</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>重组预案（2025-04-10）。若已出草案则取草案数据；若已终止，最新进展填“终止”再定是否保留</t>
+          <t>重组预案（2025-04-10）；Wind显示交易失败，未披露作价</t>
         </is>
       </c>
     </row>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -767,47 +767,47 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>688655.SH</t>
+          <t>301362.SZ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>迅捷兴</t>
+          <t>民爆光电</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>终止（Wind标注失败）</t>
+          <t>51%已完成（2026-04工商变更）；49%发股部分进行中</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>嘉之宏100%股权</t>
+          <t>厦芝精密51%股权（另49%拟发股购买）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PCB样板、小批量板</t>
+          <t>LED照明</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>柔性电路板FPC（显示模组、新能源电池）</t>
+          <t>PCB钻针（载板、AI服务器等高端钻针）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>横向整合、产品线延伸</t>
+          <t>跨界转型</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>发行股份及支付现金</t>
+          <t>51%现金；49%发行股份</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>预案未定价</t>
+          <t>24,500（51%部分）</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -825,9 +825,9 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>1,986.64（2024年）</t>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -847,59 +847,59 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>PCB制造（已终止，建议剔除或仅作参考）</t>
+          <t>PCB耗材</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>重组预案（2025-04-10）；Wind显示交易失败，未披露作价</t>
+          <t>发行股份购买资产预案（2026-01-31）及51%股权收购公告。另向标的提供不超过2亿元财务资助</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>301362.SZ</t>
+          <t>688308.SH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>民爆光电</t>
+          <t>欧科亿</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>51%已完成（2026-04工商变更）；49%发股部分进行中</t>
+          <t>框架协议（2026-05）</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>厦芝精密51%股权（另49%拟发股购买）</t>
+          <t>永鑫精工51%股权（受让+增资）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>LED照明</t>
+          <t>数控刀片、硬质合金棒材</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>PCB钻针（载板、AI服务器等高端钻针）</t>
+          <t>PCB微钻、PCB铣刀</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>跨界转型</t>
+          <t>纵向整合（棒材→钻针）</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>51%现金；49%发行股份</t>
+          <t>100%现金（受让+增资）</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>24,500（51%部分）</t>
+          <t>≤42,500（受让≤17,500+增资25,000）</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -944,54 +944,54 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>发行股份购买资产预案（2026-01-31）及51%股权收购公告。另向标的提供不超过2亿元财务资助</t>
+          <t>股权收购及增资扩股框架协议公告（2026-05-19）；增资投前估值不超过7亿元，审计评估未完成</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>688308.SH</t>
+          <t>301176.SZ</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>欧科亿</t>
+          <t>逸豪新材</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>框架协议（2026-05）</t>
+          <t>预案（2026-09，定增募资）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>永鑫精工51%股权（受让+增资）</t>
+          <t>铭丰电子不低于78%股权（增资收购）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>数控刀片、硬质合金棒材</t>
+          <t>电子电路铜箔、铝基覆铜板、PCB</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>PCB微钻、PCB铣刀</t>
+          <t>电解铜箔（HVLP、载体铜箔、锂电铜箔）</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>纵向整合（棒材→钻针）</t>
+          <t>横向整合</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>100%现金（受让+增资）</t>
+          <t>定增募资后现金增资收购</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>≤42,500（受让≤17,500+增资25,000）</t>
+          <t>募资≤180,000；标的全部股权价值约定≤50,000</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1009,81 +1009,81 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>亏损（2026H1净利润-7,800）</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>PCB耗材</t>
+          <t>PCB材料（标的净资产为负）</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>股权收购及增资扩股框架协议公告（2026-05-19）；增资投前估值不超过7亿元，审计评估未完成</t>
+          <t>向特定对象发行股票预案（2026-09-21）。2026-06末标的净资产-1.50亿元，资产负债率104.77%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>301176.SZ</t>
+          <t>603226.SH</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>逸豪新材</t>
+          <t>菲林格尔</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>预案（2026-09，定增募资）</t>
+          <t>拟收购（2026-09-18公告）</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>铭丰电子不低于78%股权（增资收购）</t>
+          <t>克锐斯51%股权</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>电子电路铜箔、铝基覆铜板、PCB</t>
+          <t>地板等家居产品</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>电解铜箔（HVLP、载体铜箔、锂电铜箔）</t>
+          <t>PCB压合工序自动化设备（裁切机、铆钉机、预叠线）</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>横向整合</t>
+          <t>跨界转型</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>定增募资后现金增资收购</t>
+          <t>100%现金</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>募资≤180,000；标的全部股权价值约定≤50,000</t>
+          <t>21,420（暂定）</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1103,64 +1103,64 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>亏损（2026H1净利润-7,800）</t>
+          <t>509.22（2025年，未审）</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>约82.5</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>4,625.00</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>约9.08</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>PCB材料（标的净资产为负）</t>
+          <t>PCB设备</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>向特定对象发行股票预案（2026-09-21）。2026-06末标的净资产-1.50亿元，资产负债率104.77%</t>
+          <t>2026-09-18公告及上交所监管工作函。承诺2026–2029年净利润4,000/4,500/5,000/5,000万元</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>603226.SH</t>
+          <t>002860.SZ</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>菲林格尔</t>
+          <t>星帅尔</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>拟收购（2026-09-18公告）</t>
+          <t>停牌筹划（2026-09-21）</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>克锐斯51%股权</t>
+          <t>梵宇科技100%+湘鹰新材料100%股权</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>地板等家居产品</t>
+          <t>压缩机用热保护器、起动器等继电器</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PCB压合工序自动化设备（裁切机、铆钉机、预叠线）</t>
+          <t>PCB刀具设备（钻针加工中心等）及半成品耗材</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1170,185 +1170,185 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
+          <t>51%现金+49%发行股份</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>84,000（整体估值暂定）</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>7,000.00</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>约12.00</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>PCB设备/耗材</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>停牌公告（2026-09-21）。承诺2026–2028年扣非净利润5,500/7,500/8,000万元；预计不构成重大资产重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>以下为2023年以前备选（案例不够时启用）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>元盛电子76.12%股权（经珠海亿盛间接+直接收购）</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>刚性PCB、HDI</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>柔性电路板FPC</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>100%现金</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>21,420（暂定）</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>509.22（2025年，未审）</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>约82.5</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>4,625.00</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>约9.08</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>PCB设备</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18公告及上交所监管工作函。承诺2026–2029年净利润4,000/4,500/5,000/5,000万元</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>002860.SZ</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>星帅尔</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>停牌筹划（2026-09-21）</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>梵宇科技100%+湘鹰新材料100%股权</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>压缩机用热保护器、起动器等继电器</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>PCB刀具设备（钻针加工中心等）及半成品耗材</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>跨界转型</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>51%现金+49%发行股份</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>84,000（整体估值暂定）</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>7,000.00</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>约12.00</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>PCB设备/耗材</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>停牌公告（2026-09-21）。承诺2026–2028年扣非净利润5,500/7,500/8,000万元；预计不构成重大资产重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>以下为2023年以前备选（案例不够时启用）</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2017年9月30日</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>PCB制造，2018年</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>整体评估值4.56亿元；2019年再收购剩余45%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>002579.SZ</t>
+          <t>603002.SH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>宏昌电子</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1358,47 +1358,47 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>元盛电子76.12%股权（经珠海亿盛间接+直接收购）</t>
+          <t>无锡宏仁100%股权</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>刚性PCB、HDI</t>
+          <t>电子级环氧树脂</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>柔性电路板FPC</t>
+          <t>覆铜板</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>横向整合</t>
+          <t>纵向整合</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>发行股份</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>33,000</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>2017年9月30日</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>102,900</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>116.03%</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1411,114 +1411,22 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>10,000.00</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>约10.29</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>PCB制造，2018年</t>
+          <t>PCB材料，2020年</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>整体评估值4.56亿元；2019年再收购剩余45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>603002.SH</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>宏昌电子</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>无锡宏仁100%股权</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>电子级环氧树脂</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>覆铜板</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>纵向整合</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>发行股份</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>102,900</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>收益法</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>116.03%</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>10,000.00</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>约10.29</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>PCB材料，2020年</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>承诺2020–2022年扣非净利润8,600/9,400/12,000万元</t>
         </is>
@@ -1535,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1607,6 +1515,50 @@
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>标的在海外</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>688655.SH</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>迅捷兴</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>嘉之宏（FPC）100%，2025-03首次披露，发行股份及支付现金；未披露作价</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>交易已终止（Wind：失败）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>300658.SZ</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>延江股份</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>甬强科技（IC载板用覆铜板材料）98.54%，2026-01首次披露，发行股份及支付现金；未披露作价</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>交易已终止（2026-05，估值与对赌谈不拢）</t>
         </is>
       </c>
     </row>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>已完成（2023-07交割）</t>
+          <t>已完成（2022-12-16公告，2023-07交割）</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>HDI/类载板（手机主板等）</t>
+          <t>高密度互连板（HDI、Anylayer HDI）、类载板、模组基板，主要用于智能手机</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -710,37 +710,37 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>100%现金（自筹）</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>约82,700（最终159亿日元）</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>基础价87,000（176.61亿日元）；最终约82,700（159亿日元）</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>/（定价基准日2022年6月30日）</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>/（双方协商确定）</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>/（无评估；基础价÷2022-06末净资产122,208万元≈0.71倍市净率）</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-5,464（2021年，经审计）</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>不适用（亏损）</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>关于收购股权的公告（2022-12-17）。非重大资产重组，可能无评估数据</t>
+          <t>《关于收购股权的公告》（2022-12-17）：定价依据为双方协商确定，不构成重大资产重组，无业绩承诺；2022年1-6月净利润1,664万元（未审）。最终价格以交割公告为准</t>
         </is>
       </c>
     </row>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>印制电路板（TCL华星核心供应商）</t>
+          <t>印制电路板（单/双面板、多层板、HDI板、高频高速板、厚铜线圈板）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -641,24 +641,24 @@
           <t>167.32%</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>4,176.94（2022年）</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>12.84（Wind标的方PE，口径待核）</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>12.84</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>/</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Wind并购重组事件；重大资产购买及增资暨关联交易报告书（2023-09）。标的2022年净利润、有无业绩承诺待核</t>
+          <t>《重大资产购买及增资暨关联交易报告书（草案）（修订稿）》（2023-09-29）。市盈率取报告书口径：100%股权评估值53,631.86÷2022年净利润4,176.94；因含增资，不能用作价÷51%折算。无业绩承诺</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>002579.SZ</t>
+          <t>300657.SZ</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>中京电子</t>
+          <t>弘信电子</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>元盛电子76.12%股权（经珠海亿盛间接+直接收购）</t>
+          <t>华扬电子（比例待核）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>刚性PCB、HDI</t>
+          <t>柔性电路板FPC</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>柔性电路板FPC</t>
+          <t>多层板、HDI板</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1284,19 +1284,19 @@
           <t>横向整合</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>100%现金</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>33,000</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>2017年9月30日</t>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1314,9 +1314,9 @@
           <t>待Wind补</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>10.16</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1331,102 +1331,286 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>PCB制造，2018年</t>
+          <t>PCB制造，2022年</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>整体评估值4.56亿元；2019年再收购剩余45%</t>
+          <t>天津普林报告书“可比交易”表（2022-06-17）；比例、方式等待查公告</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>603386.SH</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>广东骏亚</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>牧泰莱电路（比例待核）</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>印制电路板</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>PCB样板、小批量板</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>72,800</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>12.78</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>PCB制造，2019年</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>天津普林报告书“可比交易”表（2019-08-22）；比例、方式等待查公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>002579.SZ</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>中京电子</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>元盛电子76.12%股权（经珠海亿盛间接+直接收购）</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>刚性PCB、HDI</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>柔性电路板FPC</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>横向整合</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>100%现金</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2017年9月30日</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>PCB制造，2018年</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>整体评估值4.56亿元；2019年再收购剩余45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>603002.SH</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>宏昌电子</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>无锡宏仁100%股权</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>电子级环氧树脂</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>覆铜板</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>纵向整合</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>发行股份</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>102,900</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>收益法</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>116.03%</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>10,000.00</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>约10.29</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>PCB材料，2020年</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>承诺2020–2022年扣非净利润8,600/9,400/12,000万元</t>
         </is>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -777,22 +777,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>51%已完成（2026-04工商变更）；49%发股部分进行中</t>
+          <t>51%现金已完成（2026-04）；49%发股草案修订稿（2026-07），待深交所审核</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>厦芝精密51%股权（另49%拟发股购买）</t>
+          <t>厦芝精密100%股权（51%现金+49%发行股份）</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LED照明</t>
+          <t>LED照明灯具</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>PCB钻针（载板、AI服务器等高端钻针）</t>
+          <t>PCB微型钻针</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -802,47 +802,47 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>51%现金；49%发行股份</t>
+          <t>51%现金+49%发行股份</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>24,500（51%部分）</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>48,000（51%现金24,480+49%发股23,520）</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026年1月31日</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>499.44%</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1,068.69（2025年）</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>44.91</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>3,700.00</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>12.97</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>发行股份购买资产预案（2026-01-31）及51%股权收购公告。另向标的提供不超过2亿元财务资助</t>
+          <t>《发行股份购买资产暨关联交易报告书（草案）（修订稿）》（2026-07）。评估值48,400万元；承诺2026–2028年净利润2,400/3,700/5,000万元；两步合计不构成重大资产重组</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>框架协议（2026-05）</t>
+          <t>董事会通过（2026-08-26），待股东会</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>永鑫精工51%股权（受让+增资）</t>
+          <t>永鑫精工51%股权（受让33.5%+增资）</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>PCB微钻、PCB铣刀</t>
+          <t>PCB微钻、铣刀</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -894,47 +894,47 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>100%现金（受让+增资）</t>
+          <t>100%现金（受让17,500+增资25,000）</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>≤42,500（受让≤17,500+增资25,000）</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>42,500</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026年3月31日</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>收益法</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>234.63%（按2026-03末净资产21,433.97万元计算）</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>3,310.85（2025年，经审计）</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>21.14</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>7,666.67</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>9.13</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>股权收购及增资扩股框架协议公告（2026-05-19）；增资投前估值不超过7亿元，审计评估未完成</t>
+          <t>框架协议（2026-05-20）及取得51%股权公告（2026-08）。评估值71,725.15万元；市盈率按增资投前估值7亿元计；老股综合估值5.25亿元（对赌股东6.29亿、非对赌股东4亿），按5.25亿计为15.86/6.85倍。承诺2026–2028年净利润5,500/7,500/10,000万元</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>预案（2026-09，定增募资）</t>
+          <t>定增预案（2026-09-21）</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>铭丰电子不低于78%股权（增资收购）</t>
+          <t>铭丰电子不低于78%股权（增资）</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>电解铜箔（HVLP、载体铜箔、锂电铜箔）</t>
+          <t>电解铜箔（电子电路铜箔、锂电铜箔）</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -986,37 +986,37 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>定增募资后现金增资收购</t>
+          <t>定增募资后现金增资</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>募资≤180,000；标的全部股权价值约定≤50,000</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>增资总额≤180,000；增资前全部股权价值≤50,000</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026年6月30日（评估未完成）</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>预案未披露</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>不适用（净资产为负）</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>亏损（2026H1净利润-7,800）</t>
+          <t>-16,480.49（2025年，未审）</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>不适用</t>
+          <t>不适用（亏损）</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>PCB材料（标的净资产为负）</t>
+          <t>PCB材料</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>向特定对象发行股票预案（2026-09-21）。2026-06末标的净资产-1.50亿元，资产负债率104.77%</t>
+          <t>定增预案及募集资金可行性分析报告（2026-09-21）。2026-06末净资产-15,008.52万元；预案未设业绩承诺</t>
         </is>
       </c>
     </row>

--- a/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
+++ b/output/PCB并购案例/PCB可比交易案例_初稿.xlsx
@@ -81,10 +81,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -944,7 +944,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>框架协议（2026-05-20）及取得51%股权公告（2026-08）。评估值71,725.15万元；市盈率按增资投前估值7亿元计；老股综合估值5.25亿元（对赌股东6.29亿、非对赌股东4亿），按5.25亿计为15.86/6.85倍。承诺2026–2028年净利润5,500/7,500/10,000万元</t>
+          <t>框架协议（2026-05-20）及取得51%股权公告（2026-08）。评估值71,725.15万元；市盈率按增资投前估值7亿元计；老股综合估值5.25亿元（对赌股东6.29亿、非对赌股东4亿），按5.25亿计为15.86/6.85倍；按总对价4.25亿÷51%扣除增资款2.5亿的综合投前估值约5.83亿计为17.62/7.61倍。承诺2026–2028年净利润5,500/7,500/10,000万元</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>拟收购（2026-09-18公告）</t>
+          <t>签署附条件生效协议（2026-09-18公告），审计评估未完成</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>地板等家居产品</t>
+          <t>木地板、全屋定制家居</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>PCB压合工序自动化设备（裁切机、铆钉机、预叠线）</t>
+          <t>PCB压合工序自动化设备（裁切、配板、预叠、热熔/铆钉）</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1078,27 +1078,27 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>100%现金</t>
+          <t>100%现金（受让老股）</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>21,420（暂定）</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>21,420（暂定；100%估值42,000）</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>未披露（以后续审计评估为准）</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>不适用（尚无评估；估值÷2026-06末净资产2,490.89万元≈16.9倍市净率）</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>约82.5</t>
+          <t>82.48</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>约9.08</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18公告及上交所监管工作函。承诺2026–2029年净利润4,000/4,500/5,000/5,000万元</t>
+          <t>《关于拟现金收购克锐斯51%股权的公告》（2026-09-18）。承诺2026–2029年扣非孰低净利润4,000/4,500/5,000/5,000万元；不构成重大资产重组</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>停牌筹划（2026-09-21）</t>
+          <t>停牌筹划（2026-09-22起），方案最晚10月14日前披露</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>压缩机用热保护器、起动器等继电器</t>
+          <t>压缩机用热保护器、起动器等</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PCB刀具设备（钻针加工中心等）及半成品耗材</t>
+          <t>PCB刀具设备（钻针加工设备）及半成品耗材</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1170,37 +1170,37 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>51%现金+49%发行股份</t>
+          <t>51%现金+49%发行股份，配套募资</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>84,000（整体估值暂定）</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
+          <t>84,000（两家合计估值，暂定）</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>未披露</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>约12.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>停牌公告（2026-09-21）。承诺2026–2028年扣非净利润5,500/7,500/8,000万元；预计不构成重大资产重组</t>
+          <t>停牌公告（2026-09-21）。承诺2026–2028年扣非净利润5,500/7,500/8,000万元；预计不构成重大资产重组。方案出来后补标的财务数据</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>以下为2023年以前备选（案例不够时启用）</t>
         </is>
@@ -1284,7 +1284,7 @@
           <t>横向整合</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1294,22 +1294,22 @@
           <t>39,000</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1319,12 +1319,12 @@
           <t>10.16</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1376,7 +1376,7 @@
           <t>横向整合</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1386,22 +1386,22 @@
           <t>72,800</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1411,12 +1411,12 @@
           <t>12.78</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1483,32 +1483,32 @@
           <t>2017年9月30日</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1570,7 +1570,7 @@
           <t>102,900</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
@@ -1585,12 +1585,12 @@
           <t>116.03%</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>待Wind补</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>待Wind补</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>待Wind补</t>
         </is>
